--- a/later_expandnow.xlsx
+++ b/later_expandnow.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>no specific opener found on site; bestseller (magnesium capsules) has no clear video angle; needs a better featured product</t>
+          <t>missing fill-in: opener; no specific opener found on site; bestseller (magnesium capsules) has no clear video angle; needs a better featured product</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>home country not confirmed on the brand's legal/imprint/terms page; no specific opener found on site; no featured product; no specific featured product found on site</t>
+          <t>home country not confirmed on the brand's legal/imprint/terms page; missing fill-in: product, opener; no specific opener found on site; no featured product; no specific featured product found on site</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>home country not confirmed on the brand's legal/imprint/terms page; no specific opener found on site; no featured product; no specific featured product found on site</t>
+          <t>home country not confirmed on the brand's legal/imprint/terms page; missing fill-in: product, opener; no specific opener found on site; no featured product; no specific featured product found on site</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
